--- a/data/trans_orig/P6709-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24474</t>
+          <t>24976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>47018</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>15344</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13211</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32275</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>59025</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11235</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>17758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>38659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46731</t>
+          <t>47386</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69200</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>32874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51834</t>
+          <t>52176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84668</t>
+          <t>83136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114892</t>
+          <t>113455</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>35861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24859</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>31467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>26446</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26886</t>
+          <t>25849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>22268</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46418</t>
+          <t>44865</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>27564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19735</t>
+          <t>21107</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93168</t>
+          <t>93129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120076</t>
+          <t>118961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67678</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89496</t>
+          <t>89315</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169908</t>
+          <t>168798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204308</t>
+          <t>202189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39330</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35699</t>
+          <t>35919</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59409</t>
+          <t>59927</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34853</t>
+          <t>33805</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55333</t>
+          <t>55737</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29076</t>
+          <t>29298</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50383</t>
+          <t>52382</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77720</t>
+          <t>80461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43239</t>
+          <t>43728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65534</t>
+          <t>65773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>39996</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69989</t>
+          <t>69292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99509</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13976</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23675</t>
+          <t>22991</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>16243</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37782</t>
+          <t>37124</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26720</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48886</t>
+          <t>49141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31943</t>
+          <t>32289</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47308</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74357</t>
+          <t>76141</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27767</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49291</t>
+          <t>49769</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>20343</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38835</t>
+          <t>38757</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52742</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81576</t>
+          <t>81437</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40670</t>
+          <t>39369</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64501</t>
+          <t>64186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36557</t>
+          <t>37773</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64958</t>
+          <t>64042</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95064</t>
+          <t>95746</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11787</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15627</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21426</t>
+          <t>22449</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26652</t>
+          <t>27901</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19268</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>20700</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>40316</t>
+          <t>39341</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40564</t>
+          <t>39322</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17378</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33519</t>
+          <t>34758</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>19465</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37197</t>
+          <t>37296</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>29938</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>52329</t>
+          <t>52557</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>25601</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13358</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>19410</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>42885</t>
+          <t>42394</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31372</t>
+          <t>31663</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>20227</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>45778</t>
+          <t>45843</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>49459</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>72450</t>
+          <t>72738</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>33321</t>
+          <t>33337</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>72709</t>
+          <t>74020</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>100596</t>
+          <t>100123</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32228</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>33598</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>31081</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>56645</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>32414</t>
+          <t>32443</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>53102</t>
+          <t>52957</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>82278</t>
+          <t>82982</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>55427</t>
+          <t>54755</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>88375</t>
+          <t>89934</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>128297</t>
+          <t>128663</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>54175</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>84632</t>
+          <t>84734</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>48280</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>87038</t>
+          <t>86996</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>124010</t>
+          <t>123291</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>88017</t>
+          <t>85553</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>120180</t>
+          <t>119592</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>57611</t>
+          <t>57453</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>83911</t>
+          <t>83985</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>151483</t>
+          <t>154059</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>195886</t>
+          <t>199553</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>27662</t>
+          <t>28967</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>21039</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>46417</t>
+          <t>46672</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>33588</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>31393</t>
+          <t>29931</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>29310</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>55520</t>
+          <t>56566</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>69007</t>
+          <t>67813</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101584</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>44991</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>74474</t>
+          <t>72133</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>119853</t>
+          <t>122723</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>163773</t>
+          <t>164502</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>117624</t>
+          <t>118722</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>155346</t>
+          <t>157921</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>64539</t>
+          <t>64936</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>95760</t>
+          <t>94916</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>191949</t>
+          <t>192520</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>242439</t>
+          <t>241535</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>84174</t>
+          <t>85587</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>121187</t>
+          <t>120503</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>71057</t>
+          <t>70959</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>104553</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>165655</t>
+          <t>165498</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>213401</t>
+          <t>214300</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>79594</t>
+          <t>78148</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>120522</t>
+          <t>118399</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>75015</t>
+          <t>71686</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>110813</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>160064</t>
+          <t>163329</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>217943</t>
+          <t>219252</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>80968</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>121206</t>
+          <t>119531</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>52296</t>
+          <t>51743</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>88417</t>
+          <t>88337</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>142534</t>
+          <t>141974</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>194745</t>
+          <t>195651</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>265252</t>
+          <t>264048</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>328253</t>
+          <t>329847</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>167984</t>
+          <t>169162</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>223492</t>
+          <t>223138</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>452047</t>
+          <t>449692</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>536118</t>
+          <t>533137</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>324434</t>
+          <t>323291</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>393412</t>
+          <t>393347</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>184042</t>
+          <t>186191</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>241139</t>
+          <t>237077</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>523479</t>
+          <t>525727</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>610284</t>
+          <t>606867</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>526027</t>
+          <t>526995</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>603274</t>
+          <t>603724</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>341515</t>
+          <t>343983</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>405039</t>
+          <t>405738</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>890026</t>
+          <t>893456</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>988726</t>
+          <t>989120</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016</t>
+          <t>Población según si tiene influencia sobre el orden en el que realizan las tareas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54050</t>
+          <t>54481</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17192</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34964</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53491</t>
+          <t>50991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82898</t>
+          <t>81468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21499</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17588</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37146</t>
+          <t>37986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12098</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29749</t>
+          <t>29804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>18305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40253</t>
+          <t>38600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21227</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>42134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>35187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56720</t>
+          <t>57699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52256</t>
+          <t>51777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73007</t>
+          <t>73587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104391</t>
+          <t>103949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29469</t>
+          <t>29696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11720</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28392</t>
+          <t>27877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27911</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>52135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32999</t>
+          <t>33659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>19800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>23787</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47349</t>
+          <t>46824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24334</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44807</t>
+          <t>44850</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18552</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47656</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76540</t>
+          <t>77234</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>24250</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44565</t>
+          <t>46472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>17845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58226</t>
+          <t>56089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48726</t>
+          <t>48205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74280</t>
+          <t>74364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57004</t>
+          <t>57116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91496</t>
+          <t>90105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124236</t>
+          <t>124120</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>24347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37172</t>
+          <t>36786</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>23413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45381</t>
+          <t>43386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>29473</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49735</t>
+          <t>49061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28715</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47503</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72771</t>
+          <t>72316</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42140</t>
+          <t>41547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>39451</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49999</t>
+          <t>49305</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76578</t>
+          <t>74960</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>27217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20847</t>
+          <t>21961</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41423</t>
+          <t>41678</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23519</t>
+          <t>23410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36790</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20996</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>27912</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>19034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41395</t>
+          <t>41872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20805</t>
+          <t>20167</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19189</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38688</t>
+          <t>39537</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44523</t>
+          <t>46035</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67151</t>
+          <t>66739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49401</t>
+          <t>48932</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>82937</t>
+          <t>81920</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111375</t>
+          <t>111159</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>907</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23059</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25173</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39599</t>
+          <t>39219</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>61084</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20843</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>35216</t>
+          <t>33880</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>56298</t>
+          <t>55060</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>24232</t>
+          <t>23389</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>33211</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>22537</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>27854</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>51073</t>
+          <t>50298</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>32898</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21513</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>37537</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>41750</t>
+          <t>40331</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>67296</t>
+          <t>65274</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>40580</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28323</t>
+          <t>28114</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>37866</t>
+          <t>39630</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>62380</t>
+          <t>64781</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>37026</t>
+          <t>35581</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>47784</t>
+          <t>48396</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>68555</t>
+          <t>67900</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>22137</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43873</t>
+          <t>44677</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>68478</t>
+          <t>69476</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>105148</t>
+          <t>105330</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>46613</t>
+          <t>47659</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>76828</t>
+          <t>77402</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>46811</t>
+          <t>45782</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>72441</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>99857</t>
+          <t>102519</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>141851</t>
+          <t>144934</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>101770</t>
+          <t>102899</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>141104</t>
+          <t>143171</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>77366</t>
+          <t>77075</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>109107</t>
+          <t>107824</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>190899</t>
+          <t>188436</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>240672</t>
+          <t>239542</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>40678</t>
+          <t>41522</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>72044</t>
+          <t>70651</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>27006</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>50650</t>
+          <t>51151</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>75142</t>
+          <t>76487</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>111907</t>
+          <t>113319</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>55223</t>
+          <t>53542</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>89721</t>
+          <t>86974</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>47926</t>
+          <t>48103</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>77691</t>
+          <t>77216</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>110733</t>
+          <t>111121</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>154200</t>
+          <t>153654</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14936</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>39094</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>37957</t>
+          <t>36989</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>40573</t>
+          <t>39229</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>69876</t>
+          <t>67638</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>72435</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>104350</t>
+          <t>103831</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>42665</t>
+          <t>44317</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>68722</t>
+          <t>69563</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>123102</t>
+          <t>122614</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>164474</t>
+          <t>163778</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>94378</t>
+          <t>95725</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>129083</t>
+          <t>130871</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>79831</t>
+          <t>81861</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>110708</t>
+          <t>112907</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>184044</t>
+          <t>185994</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>228725</t>
+          <t>229472</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>80275</t>
+          <t>77518</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>112513</t>
+          <t>113031</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>46048</t>
+          <t>45994</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>73803</t>
+          <t>72525</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>133402</t>
+          <t>133341</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>176438</t>
+          <t>176739</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>130460</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>181842</t>
+          <t>177202</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>90577</t>
+          <t>93070</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>129420</t>
+          <t>131500</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>235043</t>
+          <t>233025</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>294609</t>
+          <t>299007</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>162647</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>214470</t>
+          <t>216988</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>126839</t>
+          <t>129095</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>170905</t>
+          <t>176792</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>301717</t>
+          <t>303796</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>373570</t>
+          <t>373233</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>343032</t>
+          <t>342700</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>412705</t>
+          <t>411205</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>238166</t>
+          <t>238857</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>290770</t>
+          <t>294122</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>602069</t>
+          <t>596678</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>691261</t>
+          <t>686570</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>285910</t>
+          <t>290987</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>352403</t>
+          <t>353453</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>209617</t>
+          <t>210796</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>261602</t>
+          <t>266907</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>515673</t>
+          <t>518572</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>597537</t>
+          <t>603207</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>350384</t>
+          <t>348712</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>419491</t>
+          <t>421042</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>250980</t>
+          <t>247956</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>306705</t>
+          <t>304775</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>615537</t>
+          <t>613060</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>705161</t>
+          <t>704282</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6709-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6709-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47018</t>
+          <t>47853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>15069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30977</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30929</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>33664</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59025</t>
+          <t>57165</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>28011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38659</t>
+          <t>37639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47386</t>
+          <t>45889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68784</t>
+          <t>68818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52176</t>
+          <t>52807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83136</t>
+          <t>83923</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113455</t>
+          <t>113057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25517</t>
+          <t>24184</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35861</t>
+          <t>36375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24396</t>
+          <t>24972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31467</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26446</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25849</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44865</t>
+          <t>46432</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27564</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21107</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93129</t>
+          <t>94056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118961</t>
+          <t>119650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66607</t>
+          <t>67701</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89315</t>
+          <t>88789</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>168798</t>
+          <t>168906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202189</t>
+          <t>202844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17384</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26192</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>20966</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>39887</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25805</t>
+          <t>25815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>35180</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59927</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33805</t>
+          <t>34770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>55651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29298</t>
+          <t>29121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52382</t>
+          <t>52622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80461</t>
+          <t>78916</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43728</t>
+          <t>43513</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65773</t>
+          <t>64891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39996</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69292</t>
+          <t>69179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98194</t>
+          <t>98533</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>14142</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>16887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22991</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>25420</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16243</t>
+          <t>16682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37124</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>27731</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49141</t>
+          <t>49230</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>32801</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>48164</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>76141</t>
+          <t>75536</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27161</t>
+          <t>28191</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49769</t>
+          <t>49679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20343</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38757</t>
+          <t>38788</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52962</t>
+          <t>52662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81437</t>
+          <t>79764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39369</t>
+          <t>39492</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64186</t>
+          <t>63751</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>37096</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64042</t>
+          <t>66339</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95746</t>
+          <t>98026</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27901</t>
+          <t>26178</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>19657</t>
+          <t>19188</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>27218</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39322</t>
+          <t>39891</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>34758</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>19947</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37296</t>
+          <t>37529</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29938</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>52557</t>
+          <t>52999</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25601</t>
+          <t>25784</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13546</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>31821</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14522</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>19818</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>24686</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>45843</t>
+          <t>46396</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>49459</t>
+          <t>49896</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>72738</t>
+          <t>72878</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>33337</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>74020</t>
+          <t>74416</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>100123</t>
+          <t>102665</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32265</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>15325</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>32594</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>56645</t>
+          <t>57196</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>22344</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>33094</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>52957</t>
+          <t>53309</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>83327</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>30299</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>54755</t>
+          <t>55586</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>89934</t>
+          <t>88649</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>128663</t>
+          <t>128190</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>53006</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>84734</t>
+          <t>82986</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>48909</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>86996</t>
+          <t>85315</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>123291</t>
+          <t>123504</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>85553</t>
+          <t>85973</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>119592</t>
+          <t>120460</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>57453</t>
+          <t>57587</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>83985</t>
+          <t>84435</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>154059</t>
+          <t>154568</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>199553</t>
+          <t>197472</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>25758</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>21039</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>46672</t>
+          <t>45894</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>13874</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>33706</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>29931</t>
+          <t>29666</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>28803</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>56744</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>67813</t>
+          <t>68730</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>101584</t>
+          <t>100592</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>45139</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>72133</t>
+          <t>72007</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>122723</t>
+          <t>121727</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>164502</t>
+          <t>165152</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>118722</t>
+          <t>117176</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>157921</t>
+          <t>155493</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>64936</t>
+          <t>65968</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>94916</t>
+          <t>96874</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>192520</t>
+          <t>193723</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>241535</t>
+          <t>243670</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>85587</t>
+          <t>84233</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>120503</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>70959</t>
+          <t>72424</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>104553</t>
+          <t>104882</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>165498</t>
+          <t>164409</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>214300</t>
+          <t>212570</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>78148</t>
+          <t>78124</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>118399</t>
+          <t>120454</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>72877</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>110813</t>
+          <t>110186</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>163329</t>
+          <t>160822</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>219252</t>
+          <t>217210</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>79240</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>119531</t>
+          <t>120294</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>51743</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>88337</t>
+          <t>86770</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>141974</t>
+          <t>146056</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>195651</t>
+          <t>197377</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>264048</t>
+          <t>266200</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>329847</t>
+          <t>329156</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>169162</t>
+          <t>170709</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>223138</t>
+          <t>224412</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>449692</t>
+          <t>450901</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>533137</t>
+          <t>535863</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>323291</t>
+          <t>323562</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>393347</t>
+          <t>389976</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>186581</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>237077</t>
+          <t>236972</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>525727</t>
+          <t>524110</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>606867</t>
+          <t>609941</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>526995</t>
+          <t>527795</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>603724</t>
+          <t>605674</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>343983</t>
+          <t>340818</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>405738</t>
+          <t>404481</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>893456</t>
+          <t>889055</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>989120</t>
+          <t>987087</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54481</t>
+          <t>54296</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>35402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50991</t>
+          <t>52830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81468</t>
+          <t>82725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19850</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37986</t>
+          <t>36492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>29597</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38600</t>
+          <t>40025</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>24071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42134</t>
+          <t>39729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>34037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57699</t>
+          <t>57889</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>30031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73587</t>
+          <t>72209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103949</t>
+          <t>103099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29696</t>
+          <t>30320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>27648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52135</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14467</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33659</t>
+          <t>33199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>23933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46824</t>
+          <t>46982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44850</t>
+          <t>46576</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>36217</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48182</t>
+          <t>49436</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77234</t>
+          <t>75523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46472</t>
+          <t>44919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17845</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31685</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56089</t>
+          <t>56812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48205</t>
+          <t>47308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74364</t>
+          <t>72695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>36311</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57116</t>
+          <t>56416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90105</t>
+          <t>91441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124120</t>
+          <t>123015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24347</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36786</t>
+          <t>36931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14764</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31339</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>24099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43386</t>
+          <t>45057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29473</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49061</t>
+          <t>50355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>47821</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72316</t>
+          <t>71837</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23090</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41547</t>
+          <t>41474</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21597</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49305</t>
+          <t>48836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74960</t>
+          <t>75270</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27217</t>
+          <t>26979</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41678</t>
+          <t>41091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23410</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>19616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17419</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37426</t>
+          <t>36271</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>22637</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27912</t>
+          <t>28006</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>42147</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24673</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20167</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19551</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39537</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46035</t>
+          <t>44680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66739</t>
+          <t>66948</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>31151</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48932</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81920</t>
+          <t>83208</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111159</t>
+          <t>110316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29436</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40307</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12253</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61084</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37220</t>
+          <t>37930</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24019</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>33880</t>
+          <t>35123</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>55060</t>
+          <t>56963</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23389</t>
+          <t>23258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33211</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22537</t>
+          <t>23154</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27854</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>50298</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>33925</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>22107</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>37537</t>
+          <t>37970</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>40331</t>
+          <t>40764</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>65274</t>
+          <t>65843</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>40580</t>
+          <t>40982</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>39630</t>
+          <t>38779</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>64781</t>
+          <t>62777</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>18103</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>35581</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>16427</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>48396</t>
+          <t>48533</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>39717</t>
+          <t>39892</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>67900</t>
+          <t>67765</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>44677</t>
+          <t>45689</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>69476</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>105330</t>
+          <t>105169</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>47659</t>
+          <t>48081</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>77402</t>
+          <t>76922</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>73379</t>
+          <t>72929</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>102519</t>
+          <t>101595</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>144934</t>
+          <t>143666</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>102899</t>
+          <t>102531</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>143171</t>
+          <t>144471</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>77075</t>
+          <t>76987</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>107824</t>
+          <t>108476</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>188436</t>
+          <t>189998</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>239542</t>
+          <t>239854</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>41522</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>70651</t>
+          <t>71080</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>51151</t>
+          <t>51168</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>76487</t>
+          <t>74878</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>113319</t>
+          <t>112771</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>53542</t>
+          <t>54176</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>86974</t>
+          <t>86594</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>48103</t>
+          <t>48209</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>77216</t>
+          <t>75588</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>111121</t>
+          <t>112697</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>153654</t>
+          <t>156017</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>14936</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>39138</t>
+          <t>38900</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>36989</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>39229</t>
+          <t>39497</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>67638</t>
+          <t>67505</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>72435</t>
+          <t>72246</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>103831</t>
+          <t>105052</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>42821</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>69563</t>
+          <t>68456</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>122614</t>
+          <t>122037</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>163778</t>
+          <t>163193</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>95725</t>
+          <t>93653</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>130871</t>
+          <t>128959</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>81861</t>
+          <t>81421</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>112907</t>
+          <t>110666</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>185994</t>
+          <t>182297</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>229472</t>
+          <t>229150</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>77518</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>113031</t>
+          <t>115907</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>45994</t>
+          <t>46107</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>72525</t>
+          <t>72867</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>133341</t>
+          <t>133093</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>176739</t>
+          <t>177640</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>130460</t>
+          <t>130973</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>177202</t>
+          <t>180669</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>93070</t>
+          <t>90551</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>131500</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>233025</t>
+          <t>233925</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>299007</t>
+          <t>294801</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>162868</t>
+          <t>164250</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>216988</t>
+          <t>215049</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>129095</t>
+          <t>128212</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>176792</t>
+          <t>174676</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>303796</t>
+          <t>306785</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>373233</t>
+          <t>377115</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>342700</t>
+          <t>341734</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>411205</t>
+          <t>409792</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>238857</t>
+          <t>236716</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>294122</t>
+          <t>294006</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>596678</t>
+          <t>598207</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>686570</t>
+          <t>686104</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>290987</t>
+          <t>289668</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>353453</t>
+          <t>351943</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>210796</t>
+          <t>210784</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>266907</t>
+          <t>264674</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>518572</t>
+          <t>514668</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>603207</t>
+          <t>596124</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>348712</t>
+          <t>350620</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>421042</t>
+          <t>417421</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,49 +13028,49 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>276004</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>249378</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>307040</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
           <t>29,6%</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>276004</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>247956</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>304775</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>26,61%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>23,91%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>616</t>
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>613060</t>
+          <t>613053</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>704282</t>
+          <t>708184</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
